--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484186_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484186_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2358</v>
+        <v>3.887</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3424</v>
+        <v>2.9375</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8934</v>
+        <v>0.9495</v>
       </c>
       <c r="G2" t="n">
         <v>2.9126</v>
@@ -610,13 +610,13 @@
         <v>1.9838</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9545</v>
+        <v>-0.3033</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5554</v>
+        <v>0.0398</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3992</v>
+        <v>-0.343</v>
       </c>
       <c r="V2" t="n">
         <v>1.2777</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.696</v>
+        <v>2.1549</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5931</v>
+        <v>1.7995</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1029</v>
+        <v>0.3554</v>
       </c>
       <c r="G3" t="n">
         <v>1.9004</v>
@@ -688,13 +688,13 @@
         <v>1.7855</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1741</v>
+        <v>-0.367</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1678</v>
+        <v>0.3742</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9937</v>
+        <v>-0.7412</v>
       </c>
       <c r="V3" t="n">
         <v>0.8198</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6545</v>
+        <v>1.7869</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2464</v>
+        <v>1.5752</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4081</v>
+        <v>0.2117</v>
       </c>
       <c r="G4" t="n">
         <v>2.1421</v>
@@ -766,13 +766,13 @@
         <v>2.1822</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2273</v>
+        <v>-0.095</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0567</v>
+        <v>0.3855</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2841</v>
+        <v>-0.4804</v>
       </c>
       <c r="V4" t="n">
         <v>-1.4505</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. GANDOL COBO</t>
+          <t>D. GUILLEN VIVES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6606</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.318</v>
+        <v>-0.7308</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3425</v>
+        <v>1.4884</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8714</v>
+        <v>-0.772</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.2148</v>
+        <v>-1.8097</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3433</v>
+        <v>1.0377</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4189</v>
+        <v>-0.8717</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6197</v>
+        <v>-0.9572000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2008</v>
+        <v>0.0854</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4525</v>
+        <v>0.0998</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5951</v>
+        <v>-0.8525</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1425</v>
+        <v>0.9523</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5871</v>
+        <v>0.3968</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1903</v>
       </c>
       <c r="R5" t="n">
         <v>1.5871</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5481</v>
+        <v>-0.7482</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7369</v>
+        <v>0.1248</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1888</v>
+        <v>-0.873</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6032</v>
+        <v>1.881</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6032</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. GUILLEN VIVES</t>
+          <t>E. GANDOL COBO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1913</v>
+        <v>0.0827</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.343</v>
+        <v>-0.2318</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1517</v>
+        <v>0.3145</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.772</v>
+        <v>-0.8714</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.8097</v>
+        <v>-1.2148</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0377</v>
+        <v>0.3433</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8717</v>
+        <v>-0.4189</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9572000000000001</v>
+        <v>-0.6197</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0854</v>
+        <v>0.2008</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0998</v>
+        <v>-0.4525</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8525</v>
+        <v>-0.5951</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9523</v>
+        <v>0.1425</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3968</v>
+        <v>1.5871</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1903</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>1.5871</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.6971</v>
+        <v>-0.0297</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4874</v>
+        <v>0.1871</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.2096</v>
+        <v>-0.2168</v>
       </c>
       <c r="V6" t="n">
-        <v>1.881</v>
+        <v>-0.6032</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6745</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. BONAZEBI LOUSSAKOU</t>
+          <t>A. AMABILINO PEREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7961</v>
+        <v>-1.7995</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7974</v>
+        <v>-0.2041</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0013</v>
+        <v>-1.5954</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1553</v>
+        <v>-0.1524</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4183</v>
+        <v>-0.5747</v>
       </c>
       <c r="I7" t="n">
-        <v>0.263</v>
+        <v>0.4223</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3125</v>
+        <v>1.6773</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.433</v>
+        <v>1.1449</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1205</v>
+        <v>0.5323</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1572</v>
+        <v>-1.8297</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0147</v>
+        <v>-1.7197</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1425</v>
+        <v>-0.11</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.579</v>
+        <v>-3.5709</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9758</v>
+        <v>-5.158</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3968</v>
+        <v>1.5871</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4701</v>
+        <v>-0.0312</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4908</v>
+        <v>0.669</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9792999999999999</v>
+        <v>-0.7002</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.532</v>
+        <v>1.955</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.6076</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.532</v>
+        <v>-0.6526</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. AMABILINO PEREZ</t>
+          <t>R. SOLIVELLES MENDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3704</v>
+        <v>-1.9026</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0566</v>
+        <v>-3.1321</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4271</v>
+        <v>1.2295</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1524</v>
+        <v>-1.8842</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5747</v>
+        <v>-2.4748</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4223</v>
+        <v>0.5906</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6773</v>
+        <v>-2.1856</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1449</v>
+        <v>-1.9599</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5323</v>
+        <v>-0.2257</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8297</v>
+        <v>0.3014</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.7197</v>
+        <v>-0.5148</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.11</v>
+        <v>0.8162</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.5709</v>
+        <v>0.3968</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5.158</v>
+        <v>-1.1903</v>
       </c>
       <c r="R8" t="n">
         <v>1.5871</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3979</v>
+        <v>-0.4152</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9297</v>
+        <v>0.2438</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5318000000000001</v>
+        <v>-0.659</v>
       </c>
       <c r="V8" t="n">
-        <v>1.955</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.6076</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6526</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6787</v>
+        <v>-1.9993</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9846</v>
+        <v>-1.3895</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.694</v>
+        <v>-0.6099</v>
       </c>
       <c r="G9" t="n">
         <v>-1.9173</v>
@@ -1156,13 +1156,13 @@
         <v>0.7935</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9699</v>
+        <v>-0.2905</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2494</v>
+        <v>0.3458</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7205</v>
+        <v>-0.6363</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3866</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6825</v>
+        <v>-2.1395</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6675</v>
+        <v>-0.2367</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.015</v>
+        <v>-1.9027</v>
       </c>
       <c r="G10" t="n">
         <v>0.897</v>
@@ -1234,13 +1234,13 @@
         <v>0.3968</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9285</v>
+        <v>-0.3855</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4988</v>
+        <v>-0.068</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4297</v>
+        <v>-0.3175</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0639</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. SOLIVELLES MENDEZ</t>
+          <t>C. BONAZEBI LOUSSAKOU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0173</v>
+        <v>-2.4274</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0503</v>
+        <v>-2.7554</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0331</v>
+        <v>0.328</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8842</v>
+        <v>-0.1553</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.4748</v>
+        <v>-0.4183</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5906</v>
+        <v>0.263</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.1856</v>
+        <v>-0.3125</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.9599</v>
+        <v>-0.433</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.2257</v>
+        <v>0.1205</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3014</v>
+        <v>0.1572</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5148</v>
+        <v>0.0147</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8162</v>
+        <v>0.1425</v>
       </c>
       <c r="P11" t="n">
+        <v>-2.579</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-2.9758</v>
+      </c>
+      <c r="R11" t="n">
         <v>0.3968</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-1.1903</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.5871</v>
-      </c>
       <c r="S11" t="n">
-        <v>-1.5298</v>
+        <v>0.8389</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6744</v>
+        <v>0.5329</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8554</v>
+        <v>0.306</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0089</v>
+        <v>-4.4272</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.343</v>
+        <v>-3.6491</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6659</v>
+        <v>-0.7781</v>
       </c>
       <c r="G12" t="n">
         <v>-2.1996</v>
@@ -1390,13 +1390,13 @@
         <v>0.5952</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2222</v>
+        <v>-0.6405</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1191</v>
+        <v>-0.187</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3413</v>
+        <v>-0.4535</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.1424</v>
+        <v>-6.3673</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.9004</v>
+        <v>-6.2656</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.242</v>
+        <v>-0.1017</v>
       </c>
       <c r="G13" t="n">
         <v>-4.0375</v>
@@ -1468,13 +1468,13 @@
         <v>1.3887</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3972</v>
+        <v>-0.6221</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8728</v>
+        <v>-0.238</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5243</v>
+        <v>-0.3841</v>
       </c>
       <c r="V13" t="n">
         <v>-0.1206</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.6407</v>
+        <v>-12.3937</v>
       </c>
       <c r="E14" t="n">
-        <v>-13.5297</v>
+        <v>-12.2829</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1110000000000003</v>
+        <v>-0.1107999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.137599999999999</v>
+        <v>-4.137600000000001</v>
       </c>
       <c r="H14" t="n">
         <v>-10.7122</v>
@@ -1519,7 +1519,7 @@
         <v>6.574299999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>2.569000000000001</v>
+        <v>2.568999999999999</v>
       </c>
       <c r="K14" t="n">
         <v>-1.8349</v>
@@ -1534,10 +1534,10 @@
         <v>-8.877299999999998</v>
       </c>
       <c r="O14" t="n">
-        <v>2.1705</v>
+        <v>2.170500000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>-6.943399999999999</v>
+        <v>-6.9434</v>
       </c>
       <c r="Q14" t="n">
         <v>-22.8141</v>
@@ -1546,13 +1546,13 @@
         <v>15.8709</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.3363</v>
+        <v>-3.0893</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1628</v>
+        <v>2.4099</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.499100000000001</v>
+        <v>-5.499</v>
       </c>
       <c r="V14" t="n">
         <v>1.7767</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>10.149</v>
+        <v>10.8233</v>
       </c>
       <c r="E15" t="n">
-        <v>5.3552</v>
+        <v>5.8654</v>
       </c>
       <c r="F15" t="n">
-        <v>4.7938</v>
+        <v>4.9579</v>
       </c>
       <c r="G15" t="n">
         <v>2.821</v>
@@ -1624,13 +1624,13 @@
         <v>4.1661</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2171</v>
+        <v>0.8913</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1985</v>
+        <v>0.7087</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0186</v>
+        <v>0.1827</v>
       </c>
       <c r="V15" t="n">
         <v>2.9449</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.9219</v>
+        <v>8.8971</v>
       </c>
       <c r="E16" t="n">
-        <v>4.0476</v>
+        <v>4.3537</v>
       </c>
       <c r="F16" t="n">
-        <v>3.8743</v>
+        <v>4.5434</v>
       </c>
       <c r="G16" t="n">
         <v>6.328</v>
@@ -1702,13 +1702,13 @@
         <v>3.7693</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5288</v>
+        <v>0.4464</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4593</v>
+        <v>0.7653</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9881</v>
+        <v>-0.319</v>
       </c>
       <c r="V16" t="n">
         <v>0.3373</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.1933</v>
+        <v>3.1357</v>
       </c>
       <c r="E17" t="n">
-        <v>2.019</v>
+        <v>0.3865</v>
       </c>
       <c r="F17" t="n">
-        <v>3.1743</v>
+        <v>2.7492</v>
       </c>
       <c r="G17" t="n">
         <v>1.9053</v>
@@ -1780,13 +1780,13 @@
         <v>3.5709</v>
       </c>
       <c r="S17" t="n">
-        <v>3.8316</v>
+        <v>1.7741</v>
       </c>
       <c r="T17" t="n">
-        <v>3.2934</v>
+        <v>1.6609</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5383</v>
+        <v>0.1132</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9405</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.5671</v>
+        <v>2.4013</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9159</v>
+        <v>0.6098</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6512</v>
+        <v>1.7915</v>
       </c>
       <c r="G18" t="n">
         <v>0.7419</v>
@@ -1858,13 +1858,13 @@
         <v>1.9838</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1705</v>
+        <v>1.0047</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9467</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2238</v>
+        <v>0.3641</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3373</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0009</v>
+        <v>0.8469</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8415</v>
+        <v>-1.8212</v>
       </c>
       <c r="F19" t="n">
-        <v>2.8406</v>
+        <v>2.668</v>
       </c>
       <c r="G19" t="n">
         <v>-1.5302</v>
@@ -1936,13 +1936,13 @@
         <v>4.1661</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1378</v>
+        <v>0.7099</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4193</v>
+        <v>0.601</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2815</v>
+        <v>0.109</v>
       </c>
       <c r="V19" t="n">
         <v>1.6671</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.091</v>
+        <v>0.011</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.08450000000000001</v>
+        <v>0.0175</v>
       </c>
       <c r="F20" t="n">
         <v>-0.0065</v>
@@ -2014,10 +2014,10 @@
         <v>0.1984</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3344</v>
+        <v>-0.2324</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1247</v>
+        <v>-0.0227</v>
       </c>
       <c r="U20" t="n">
         <v>-0.2097</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1293</v>
+        <v>-0.3046</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3772</v>
+        <v>-1.9691</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2479</v>
+        <v>1.6645</v>
       </c>
       <c r="G21" t="n">
         <v>-0.4034</v>
@@ -2092,13 +2092,13 @@
         <v>2.579</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0316</v>
+        <v>-0.2069</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0057</v>
+        <v>0.4139</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.0373</v>
+        <v>-0.6207</v>
       </c>
       <c r="V21" t="n">
         <v>-1.083</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7068</v>
+        <v>-2.5511</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5903</v>
+        <v>-3.1822</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8836000000000001</v>
+        <v>0.6311</v>
       </c>
       <c r="G23" t="n">
         <v>-0.5327</v>
@@ -2248,13 +2248,13 @@
         <v>1.1903</v>
       </c>
       <c r="S23" t="n">
-        <v>0.183</v>
+        <v>0.3387</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5498</v>
+        <v>-0.1416</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7328</v>
+        <v>0.4803</v>
       </c>
       <c r="V23" t="n">
         <v>-2.5555</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. AGUILERA MELCHOR</t>
+          <t>A. MONTALBÁN PÉREZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.132</v>
+        <v>-3.3403</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7499</v>
+        <v>-2.2011</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3821</v>
+        <v>-1.1392</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.8118</v>
+        <v>-2.6999</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6199</v>
+        <v>-0.1411</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.1918</v>
+        <v>-2.5587</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5592</v>
+        <v>-1.2999</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.5592</v>
+        <v>0.0605</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>-1.3604</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.2525</v>
+        <v>-1.4</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.0607</v>
+        <v>-0.2016</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.1918</v>
+        <v>-1.1983</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.3887</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.1822</v>
+        <v>-1.1903</v>
       </c>
       <c r="R24" t="n">
-        <v>0.7935</v>
+        <v>0.3968</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6717</v>
+        <v>0.1531</v>
       </c>
       <c r="T24" t="n">
-        <v>1.1224</v>
+        <v>0.2891</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4506</v>
+        <v>-0.136</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.8692</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.4724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. MONTALBÁN PÉREZ</t>
+          <t>A. AGUILERA MELCHOR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.1363</v>
+        <v>-3.6039</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.9971</v>
+        <v>-1.3621</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1392</v>
+        <v>-2.2418</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.6999</v>
+        <v>-1.8118</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1411</v>
+        <v>-0.6199</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.5587</v>
+        <v>-1.1918</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.2999</v>
+        <v>-0.5592</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0605</v>
+        <v>-0.5592</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.3604</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.4</v>
+        <v>-1.2525</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.2016</v>
+        <v>-0.0607</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.1983</v>
+        <v>-1.1918</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.7935</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1903</v>
+        <v>-2.1822</v>
       </c>
       <c r="R25" t="n">
-        <v>0.3968</v>
+        <v>0.7935</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3571</v>
+        <v>0.1998</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4932</v>
+        <v>0.5102</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.136</v>
+        <v>-0.3104</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>0.8692</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>13.6406</v>
+        <v>14.321</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1108999999999996</v>
+        <v>0.1109000000000011</v>
       </c>
       <c r="F26" t="n">
-        <v>13.5298</v>
+        <v>14.21</v>
       </c>
       <c r="G26" t="n">
         <v>4.137600000000001</v>
@@ -2482,13 +2482,13 @@
         <v>22.8142</v>
       </c>
       <c r="S26" t="n">
-        <v>4.3361</v>
+        <v>5.016400000000001</v>
       </c>
       <c r="T26" t="n">
         <v>5.4991</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.1627</v>
+        <v>-0.4825000000000001</v>
       </c>
       <c r="V26" t="n">
         <v>-1.7767</v>
